--- a/.doc/duty_speed.xlsx
+++ b/.doc/duty_speed.xlsx
@@ -2,51 +2,30 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itgz2\Desktop\BetaRobot\.doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA089091-2AB4-419C-8BD2-8E3D45D20312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B910DB-1FB3-4A7C-A0AE-CE5BC6BA95FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{862097A3-5E72-4A33-9EC1-C43CADF5CCC5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>占空比(%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>转速(rad/s)</t>
-  </si>
-  <si>
-    <t>转速(rad/s)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -92,10 +71,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -111,6 +91,1225 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>转速(rad/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$45</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="44"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$45</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="44"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.05</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.149999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19.95</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>26.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>29.15</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>35.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>38.65</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>40.450000000000003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>42.55</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>44.55</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46.75</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>48.95</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>50.6</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>52.3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>54.05</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>55.95</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>57.45</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>59.05</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>60.25</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>61.8</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>63.3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>64.55</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>66.05</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>67.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>69.05</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>70.55</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>71.349999999999994</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>78.150000000000006</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>84.2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>89.4</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>93.15</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>101.15</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>113.8</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>122.05</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-60D1-4EBB-B4D6-517099C0C146}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2041019888"/>
+        <c:axId val="2041017008"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2041019888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2041017008"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2041017008"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2041019888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>326571</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>3628</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>116114</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F270143-41BF-3DC2-C180-70D37DD5B0DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,13 +1628,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5643089-0059-4554-96B4-2A0D7F317EDA}">
-  <dimension ref="A1:C46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="11.58203125" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.58203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -443,15 +1642,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
         <v>1</v>
       </c>
+      <c r="C1"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -459,487 +1656,394 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3">
-        <v>0</v>
-      </c>
+        <v>5.15</v>
+      </c>
+      <c r="C3"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>5.4</v>
-      </c>
-      <c r="C4">
-        <v>4.9000000000000004</v>
-      </c>
+        <v>7.6</v>
+      </c>
+      <c r="C4"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>7.4</v>
-      </c>
-      <c r="C5">
-        <v>7.8</v>
-      </c>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="C5"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6">
-        <v>9.5</v>
-      </c>
-      <c r="C6">
-        <v>9.9</v>
-      </c>
+        <v>11.3</v>
+      </c>
+      <c r="C6"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>11.6</v>
-      </c>
+        <v>13.2</v>
+      </c>
+      <c r="C7"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8">
-        <v>12.9</v>
-      </c>
-      <c r="C8">
-        <v>13.5</v>
-      </c>
+        <v>16.05</v>
+      </c>
+      <c r="C8"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9">
-        <v>15.8</v>
-      </c>
-      <c r="C9">
-        <v>16.3</v>
-      </c>
+        <v>18.149999999999999</v>
+      </c>
+      <c r="C9"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10">
-        <v>18</v>
-      </c>
-      <c r="C10">
-        <v>18.3</v>
-      </c>
+        <v>19.95</v>
+      </c>
+      <c r="C10"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11">
-        <v>19.7</v>
-      </c>
-      <c r="C11">
-        <v>20.2</v>
-      </c>
+        <v>22.45</v>
+      </c>
+      <c r="C11"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12">
-        <v>22.4</v>
-      </c>
-      <c r="C12">
-        <v>22.5</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C12"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13">
-        <v>25</v>
-      </c>
-      <c r="C13">
-        <v>25</v>
-      </c>
+        <v>26.8</v>
+      </c>
+      <c r="C13"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14">
-        <v>26.7</v>
-      </c>
-      <c r="C14">
-        <v>26.9</v>
-      </c>
+        <v>29.15</v>
+      </c>
+      <c r="C14"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15">
-        <v>29</v>
-      </c>
-      <c r="C15">
-        <v>29.3</v>
-      </c>
+        <v>31.5</v>
+      </c>
+      <c r="C15"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16">
-        <v>31.4</v>
-      </c>
-      <c r="C16">
-        <v>31.6</v>
-      </c>
+        <v>33.5</v>
+      </c>
+      <c r="C16"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17">
-        <v>33.4</v>
-      </c>
-      <c r="C17">
-        <v>33.6</v>
-      </c>
+        <v>35.700000000000003</v>
+      </c>
+      <c r="C17"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18">
-        <v>35.5</v>
-      </c>
-      <c r="C18">
-        <v>35.9</v>
-      </c>
+        <v>38.65</v>
+      </c>
+      <c r="C18"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19">
-        <v>38.4</v>
-      </c>
-      <c r="C19">
-        <v>38.9</v>
-      </c>
+        <v>40.450000000000003</v>
+      </c>
+      <c r="C19"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20">
-        <v>40.299999999999997</v>
-      </c>
-      <c r="C20">
-        <v>40.6</v>
-      </c>
+        <v>42.55</v>
+      </c>
+      <c r="C20"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21">
-        <v>42.4</v>
-      </c>
-      <c r="C21">
-        <v>42.7</v>
-      </c>
+        <v>44.55</v>
+      </c>
+      <c r="C21"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B22">
-        <v>44.4</v>
-      </c>
-      <c r="C22">
-        <v>44.7</v>
-      </c>
+        <v>46.75</v>
+      </c>
+      <c r="C22"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23">
-        <v>46.5</v>
-      </c>
-      <c r="C23">
-        <v>47</v>
-      </c>
+        <v>48.95</v>
+      </c>
+      <c r="C23"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B24">
-        <v>48.8</v>
-      </c>
-      <c r="C24">
-        <v>49.1</v>
-      </c>
+        <v>50.6</v>
+      </c>
+      <c r="C24"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B25">
-        <v>50.4</v>
-      </c>
-      <c r="C25">
-        <v>50.8</v>
-      </c>
+        <v>52.3</v>
+      </c>
+      <c r="C25"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B26">
-        <v>52.1</v>
-      </c>
-      <c r="C26">
-        <v>52.5</v>
-      </c>
+        <v>54.05</v>
+      </c>
+      <c r="C26"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B27">
-        <v>53.8</v>
-      </c>
-      <c r="C27">
-        <v>54.3</v>
-      </c>
+        <v>55.95</v>
+      </c>
+      <c r="C27"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28">
-        <v>55.8</v>
-      </c>
-      <c r="C28">
-        <v>56.1</v>
-      </c>
+        <v>57.45</v>
+      </c>
+      <c r="C28"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B29">
-        <v>57.3</v>
-      </c>
-      <c r="C29">
-        <v>57.6</v>
-      </c>
+        <v>59.05</v>
+      </c>
+      <c r="C29"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B30">
-        <v>58.9</v>
-      </c>
-      <c r="C30">
-        <v>59.2</v>
-      </c>
+        <v>60.25</v>
+      </c>
+      <c r="C30"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B31">
-        <v>60.2</v>
-      </c>
-      <c r="C31">
-        <v>60.3</v>
-      </c>
+        <v>61.8</v>
+      </c>
+      <c r="C31"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32">
-        <v>61.6</v>
-      </c>
-      <c r="C32">
-        <v>62</v>
-      </c>
+        <v>63.3</v>
+      </c>
+      <c r="C32"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33">
-        <v>63.1</v>
-      </c>
-      <c r="C33">
-        <v>63.5</v>
-      </c>
+        <v>64.55</v>
+      </c>
+      <c r="C33"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B34">
-        <v>64.400000000000006</v>
-      </c>
-      <c r="C34">
-        <v>64.7</v>
-      </c>
+        <v>66.05</v>
+      </c>
+      <c r="C34"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B35">
-        <v>65.900000000000006</v>
-      </c>
-      <c r="C35">
-        <v>66.2</v>
-      </c>
+        <v>67.7</v>
+      </c>
+      <c r="C35"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B36">
-        <v>67.5</v>
-      </c>
-      <c r="C36">
-        <v>67.900000000000006</v>
-      </c>
+        <v>69.05</v>
+      </c>
+      <c r="C36"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37">
-        <v>68.900000000000006</v>
-      </c>
-      <c r="C37">
-        <v>69.2</v>
-      </c>
+        <v>70.55</v>
+      </c>
+      <c r="C37"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B38">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="C38">
-        <v>70.7</v>
-      </c>
+        <v>71.349999999999994</v>
+      </c>
+      <c r="C38"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B39">
-        <v>71.2</v>
-      </c>
-      <c r="C39">
-        <v>71.5</v>
-      </c>
+        <v>78.150000000000006</v>
+      </c>
+      <c r="C39"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B40">
-        <v>78</v>
-      </c>
-      <c r="C40">
-        <v>78.3</v>
-      </c>
+        <v>84.2</v>
+      </c>
+      <c r="C40"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B41">
-        <v>84</v>
-      </c>
-      <c r="C41">
-        <v>84.4</v>
-      </c>
+        <v>89.4</v>
+      </c>
+      <c r="C41"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B42">
-        <v>89.3</v>
-      </c>
-      <c r="C42">
-        <v>89.5</v>
-      </c>
+        <v>93.15</v>
+      </c>
+      <c r="C42"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B43">
-        <v>93</v>
-      </c>
-      <c r="C43">
-        <v>93.3</v>
-      </c>
+        <v>101.15</v>
+      </c>
+      <c r="C43"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B44">
-        <v>101</v>
-      </c>
-      <c r="C44">
-        <v>101.3</v>
-      </c>
+        <v>113.8</v>
+      </c>
+      <c r="C44"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B45">
-        <v>113.6</v>
-      </c>
-      <c r="C45">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>100</v>
-      </c>
-      <c r="B46">
-        <v>121.9</v>
-      </c>
-      <c r="C46">
-        <v>122.2</v>
-      </c>
+        <v>122.05</v>
+      </c>
+      <c r="C45"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>